--- a/Day5/02_官网页面来源与审核记录.xlsx
+++ b/Day5/02_官网页面来源与审核记录.xlsx
@@ -1774,7 +1774,7 @@
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>低频更新</t>
+          <t>周期更新</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>替换原COVID-19时期开放指南</t>
+          <t>三校区楼层布局、服务窗口和基础服务内容仍有长期参考价值。开放时间具有时效性，不能据此确认当前实时开放状态；回答开放时间问题时应以图书馆最新通知或现场安排为准，并定期复核本页面。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>河海大学本科生招生章程（2024年）</t>
+          <t>河海大学本科生招生章程（2026年）</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>https://zsw.hhu.edu.cn/zhaoshengjianzhang/999.html</t>
+          <t>https://zsw.hhu.edu.cn/zhaoshengjianzhang/1037.html</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>低频更新</t>
+          <t>年度更新</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>替换原2013年招生章程</t>
+          <t>2026年现行招生章程。招生政策具有年度时效，后续应按年度复核并优先使用最新章程。原2013年页面和2024年页面已被替换。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
